--- a/manual_evaluation/functional_correctness.xlsx
+++ b/manual_evaluation/functional_correctness.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\functional\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\AI IDE Analysis\AI-IDEs-code-analysis\manual_evaluation\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050" firstSheet="4" activeTab="8"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050" firstSheet="4" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="P1_CVBuilder" sheetId="1" r:id="rId1"/>
@@ -1911,7 +1911,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
-        <v>3.5</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>38</v>
@@ -1923,7 +1923,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
-        <v>4.0999999999999996</v>
+        <v>5.2</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>39</v>
@@ -1935,7 +1935,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>40</v>

--- a/manual_evaluation/functional_correctness.xlsx
+++ b/manual_evaluation/functional_correctness.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050" firstSheet="4" activeTab="9"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050" firstSheet="3" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="P1_CVBuilder" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="230">
   <si>
     <t>Functional Requirement</t>
   </si>
@@ -164,12 +164,6 @@
     <t>Charts and suggestions for next learning step is missing.</t>
   </si>
   <si>
-    <t>Link to the flash card display is missing on detailed view.</t>
-  </si>
-  <si>
-    <t>The interface is not drag and drop for CV sections ordering.</t>
-  </si>
-  <si>
     <t>User registration (role-based)</t>
   </si>
   <si>
@@ -717,6 +711,18 @@
   </si>
   <si>
     <t>Major detail page is missing</t>
+  </si>
+  <si>
+    <t>Tracking is missing.</t>
+  </si>
+  <si>
+    <t>Bold and italic formatting does not render as italic or bold on the user side.</t>
+  </si>
+  <si>
+    <t>Date range filtering is not working properly.</t>
+  </si>
+  <si>
+    <t>Professional category selection is missing.</t>
   </si>
 </sst>
 </file>
@@ -1265,9 +1271,7 @@
       <c r="C17" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>44</v>
-      </c>
+      <c r="D17" s="3"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
@@ -1380,7 +1384,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>25</v>
@@ -1392,7 +1396,7 @@
         <v>2.1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>25</v>
@@ -1404,7 +1408,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>25</v>
@@ -1416,7 +1420,7 @@
         <v>2.1</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>25</v>
@@ -1428,7 +1432,7 @@
         <v>3.1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>25</v>
@@ -1440,7 +1444,7 @@
         <v>3.2</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>25</v>
@@ -1452,7 +1456,7 @@
         <v>3.3</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>25</v>
@@ -1464,7 +1468,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>25</v>
@@ -1476,7 +1480,7 @@
         <v>4.2</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>25</v>
@@ -1488,13 +1492,13 @@
         <v>4.3</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -1502,7 +1506,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>25</v>
@@ -1514,7 +1518,7 @@
         <v>4.5</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>25</v>
@@ -1526,7 +1530,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>25</v>
@@ -1538,7 +1542,7 @@
         <v>5.2</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>25</v>
@@ -1549,7 +1553,7 @@
         <v>5.3</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>25</v>
@@ -1560,7 +1564,7 @@
         <v>6.1</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>25</v>
@@ -1571,7 +1575,7 @@
         <v>6.2</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>25</v>
@@ -1582,7 +1586,7 @@
         <v>6.3</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>25</v>
@@ -1593,7 +1597,7 @@
         <v>6.4</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>25</v>
@@ -1604,7 +1608,7 @@
         <v>6.5</v>
       </c>
       <c r="B21" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>25</v>
@@ -1615,13 +1619,13 @@
         <v>6.6</v>
       </c>
       <c r="B22" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D22" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
@@ -1629,7 +1633,7 @@
         <v>7.1</v>
       </c>
       <c r="B23" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>25</v>
@@ -1640,7 +1644,7 @@
         <v>8.1</v>
       </c>
       <c r="B24" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>25</v>
@@ -1651,7 +1655,7 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="B25" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>25</v>
@@ -1662,7 +1666,7 @@
         <v>8.3000000000000007</v>
       </c>
       <c r="B26" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>25</v>
@@ -1673,7 +1677,7 @@
         <v>9.1</v>
       </c>
       <c r="B27" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>25</v>
@@ -1684,7 +1688,7 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="B28" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>25</v>
@@ -1695,7 +1699,7 @@
         <v>10.1</v>
       </c>
       <c r="B29" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>25</v>
@@ -1706,7 +1710,7 @@
         <v>10.199999999999999</v>
       </c>
       <c r="B30" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>25</v>
@@ -1717,7 +1721,7 @@
         <v>10.3</v>
       </c>
       <c r="B31" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>25</v>
@@ -1728,7 +1732,7 @@
         <v>10.4</v>
       </c>
       <c r="B32" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>25</v>
@@ -1739,7 +1743,7 @@
         <v>11.1</v>
       </c>
       <c r="B33" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>27</v>
@@ -1750,7 +1754,7 @@
         <v>11.2</v>
       </c>
       <c r="B34" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>27</v>
@@ -1867,9 +1871,7 @@
       <c r="C8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>43</v>
-      </c>
+      <c r="D8" s="3"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
@@ -2036,7 +2038,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>25</v>
@@ -2048,7 +2050,7 @@
         <v>1.2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>25</v>
@@ -2060,7 +2062,7 @@
         <v>1.3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>25</v>
@@ -2072,7 +2074,7 @@
         <v>2.1</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>25</v>
@@ -2084,7 +2086,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>25</v>
@@ -2096,7 +2098,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>25</v>
@@ -2108,7 +2110,7 @@
         <v>2.4</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>25</v>
@@ -2120,7 +2122,7 @@
         <v>2.5</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>25</v>
@@ -2132,7 +2134,7 @@
         <v>3.1</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>25</v>
@@ -2144,7 +2146,7 @@
         <v>3.2</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>25</v>
@@ -2156,7 +2158,7 @@
         <v>3.3</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>25</v>
@@ -2168,7 +2170,7 @@
         <v>3.4</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>25</v>
@@ -2179,13 +2181,13 @@
         <v>3.5</v>
       </c>
       <c r="B14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
@@ -2193,7 +2195,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B15" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>25</v>
@@ -2204,7 +2206,7 @@
         <v>4.2</v>
       </c>
       <c r="B16" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>25</v>
@@ -2215,7 +2217,7 @@
         <v>4.3</v>
       </c>
       <c r="B17" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>25</v>
@@ -2226,7 +2228,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="B18" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>25</v>
@@ -2237,7 +2239,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B19" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>25</v>
@@ -2248,13 +2250,13 @@
         <v>5.2</v>
       </c>
       <c r="B20" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D20" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -2262,13 +2264,13 @@
         <v>5.3</v>
       </c>
       <c r="B21" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D21" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
@@ -2276,7 +2278,7 @@
         <v>5.4</v>
       </c>
       <c r="B22" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C22" t="s">
         <v>25</v>
@@ -2287,7 +2289,7 @@
         <v>5.5</v>
       </c>
       <c r="B23" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C23" t="s">
         <v>25</v>
@@ -2298,7 +2300,7 @@
         <v>6.1</v>
       </c>
       <c r="B24" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C24" t="s">
         <v>25</v>
@@ -2309,7 +2311,7 @@
         <v>6.2</v>
       </c>
       <c r="B25" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C25" t="s">
         <v>25</v>
@@ -2320,7 +2322,7 @@
         <v>6.3</v>
       </c>
       <c r="B26" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C26" t="s">
         <v>25</v>
@@ -2331,7 +2333,7 @@
         <v>6.4</v>
       </c>
       <c r="B27" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C27" t="s">
         <v>25</v>
@@ -2371,7 +2373,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>25</v>
@@ -2383,7 +2385,7 @@
         <v>1.2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>25</v>
@@ -2395,7 +2397,7 @@
         <v>1.3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>25</v>
@@ -2407,7 +2409,7 @@
         <v>1.4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>25</v>
@@ -2419,7 +2421,7 @@
         <v>2.1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>25</v>
@@ -2431,7 +2433,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>25</v>
@@ -2443,7 +2445,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>25</v>
@@ -2455,7 +2457,7 @@
         <v>2.4</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>25</v>
@@ -2467,7 +2469,7 @@
         <v>3.1</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>25</v>
@@ -2479,7 +2481,7 @@
         <v>3.2</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>25</v>
@@ -2491,7 +2493,7 @@
         <v>3.3</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>25</v>
@@ -2503,7 +2505,7 @@
         <v>3.4</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>25</v>
@@ -2515,7 +2517,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>25</v>
@@ -2526,13 +2528,13 @@
         <v>4.2</v>
       </c>
       <c r="B15" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D15" t="s">
-        <v>73</v>
+        <v>229</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
@@ -2540,10 +2542,13 @@
         <v>4.3</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>27</v>
+      </c>
+      <c r="D16" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
@@ -2551,7 +2556,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="B17" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>25</v>
@@ -2562,7 +2567,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B18" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>25</v>
@@ -2573,7 +2578,7 @@
         <v>5.2</v>
       </c>
       <c r="B19" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>25</v>
@@ -2584,7 +2589,7 @@
         <v>5.3</v>
       </c>
       <c r="B20" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>25</v>
@@ -2624,7 +2629,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>25</v>
@@ -2636,7 +2641,7 @@
         <v>2.1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>25</v>
@@ -2648,7 +2653,7 @@
         <v>3.1</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>25</v>
@@ -2660,7 +2665,7 @@
         <v>3.2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>25</v>
@@ -2672,7 +2677,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>25</v>
@@ -2684,7 +2689,7 @@
         <v>4.2</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>25</v>
@@ -2696,7 +2701,7 @@
         <v>4.3</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>25</v>
@@ -2708,7 +2713,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>25</v>
@@ -2720,13 +2725,13 @@
         <v>5.2</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
@@ -2734,7 +2739,7 @@
         <v>6.1</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>25</v>
@@ -2746,7 +2751,7 @@
         <v>7.1</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>25</v>
@@ -2758,7 +2763,7 @@
         <v>7.2</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>25</v>
@@ -2770,7 +2775,7 @@
         <v>8.1</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>25</v>
@@ -2782,7 +2787,7 @@
         <v>9.1</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>25</v>
@@ -2847,7 +2852,7 @@
   <cols>
     <col min="2" max="2" width="25.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -2869,7 +2874,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>25</v>
@@ -2881,7 +2886,7 @@
         <v>1.2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>25</v>
@@ -2893,7 +2898,7 @@
         <v>1.3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>25</v>
@@ -2905,7 +2910,7 @@
         <v>2.1</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>25</v>
@@ -2917,7 +2922,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>25</v>
@@ -2929,7 +2934,7 @@
         <v>3.1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>25</v>
@@ -2941,7 +2946,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>25</v>
@@ -2953,7 +2958,7 @@
         <v>4.2</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>25</v>
@@ -2965,19 +2970,21 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="3"/>
+      <c r="D10" s="3" t="s">
+        <v>228</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>5.2</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>25</v>
@@ -2989,7 +2996,7 @@
         <v>6.1</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>25</v>
@@ -3001,7 +3008,7 @@
         <v>6.2</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>25</v>
@@ -3013,7 +3020,7 @@
         <v>7.1</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>25</v>
@@ -3025,7 +3032,7 @@
         <v>7.2</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>25</v>
@@ -3099,7 +3106,7 @@
   <cols>
     <col min="2" max="2" width="45.6328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="64" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -3121,7 +3128,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>25</v>
@@ -3145,7 +3152,7 @@
         <v>2.1</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>25</v>
@@ -3157,7 +3164,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>25</v>
@@ -3169,7 +3176,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>25</v>
@@ -3181,7 +3188,7 @@
         <v>2.4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>25</v>
@@ -3193,19 +3200,21 @@
         <v>3.1</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="3"/>
+      <c r="D8" s="3" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>3.2</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>25</v>
@@ -3217,7 +3226,7 @@
         <v>3.3</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>25</v>
@@ -3229,7 +3238,7 @@
         <v>3.4</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>25</v>
@@ -3241,7 +3250,7 @@
         <v>3.5</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>25</v>
@@ -3253,7 +3262,7 @@
         <v>3.6</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>25</v>
@@ -3265,7 +3274,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>25</v>
@@ -3277,7 +3286,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>25</v>
@@ -3289,7 +3298,7 @@
         <v>5.2</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>25</v>
@@ -3300,7 +3309,7 @@
         <v>6.1</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>25</v>
@@ -3311,7 +3320,7 @@
         <v>6.2</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>25</v>
@@ -3322,7 +3331,7 @@
         <v>7.1</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>25</v>
@@ -3333,7 +3342,7 @@
         <v>7.2</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>25</v>
@@ -3344,7 +3353,7 @@
         <v>7.3</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>25</v>
@@ -3355,7 +3364,7 @@
         <v>7.4</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>25</v>
@@ -3419,7 +3428,7 @@
         <v>1.3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>25</v>
@@ -3455,7 +3464,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>25</v>
@@ -3467,7 +3476,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>25</v>
@@ -3479,7 +3488,7 @@
         <v>2.4</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>25</v>
@@ -3491,7 +3500,7 @@
         <v>3.1</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>25</v>
@@ -3503,7 +3512,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>25</v>
@@ -3515,7 +3524,7 @@
         <v>4.2</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>25</v>
@@ -3527,7 +3536,7 @@
         <v>4.3</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>25</v>
@@ -3539,7 +3548,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>25</v>
@@ -3551,7 +3560,7 @@
         <v>5.2</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>25</v>
@@ -3563,7 +3572,7 @@
         <v>5.3</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>25</v>
@@ -3574,13 +3583,13 @@
         <v>5.4</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D17" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -3588,7 +3597,7 @@
         <v>5.5</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>25</v>
@@ -3599,7 +3608,7 @@
         <v>6.1</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>25</v>
@@ -3610,7 +3619,7 @@
         <v>6.2</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>25</v>
@@ -3621,7 +3630,7 @@
         <v>7.1</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>25</v>
@@ -3632,7 +3641,7 @@
         <v>7.2</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>25</v>
@@ -3643,7 +3652,7 @@
         <v>7.3</v>
       </c>
       <c r="B23" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>25</v>
@@ -3654,7 +3663,7 @@
         <v>7.4</v>
       </c>
       <c r="B24" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>25</v>
@@ -3665,7 +3674,7 @@
         <v>8.1</v>
       </c>
       <c r="B25" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>25</v>
@@ -3676,7 +3685,7 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="B26" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>25</v>
@@ -3687,7 +3696,7 @@
         <v>8.3000000000000007</v>
       </c>
       <c r="B27" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>25</v>
@@ -3727,7 +3736,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>25</v>
@@ -3739,7 +3748,7 @@
         <v>1.2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>25</v>
@@ -3751,7 +3760,7 @@
         <v>2.1</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>25</v>
@@ -3763,13 +3772,13 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -3777,7 +3786,7 @@
         <v>3.1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>25</v>
@@ -3789,13 +3798,13 @@
         <v>3.2</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
@@ -3803,7 +3812,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>25</v>
@@ -3815,7 +3824,7 @@
         <v>4.2</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>25</v>
@@ -3827,7 +3836,7 @@
         <v>4.3</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>25</v>
@@ -3839,7 +3848,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>25</v>
@@ -3851,7 +3860,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>25</v>
@@ -3863,7 +3872,7 @@
         <v>5.2</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>25</v>
@@ -3875,7 +3884,7 @@
         <v>5.3</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>25</v>
@@ -3887,7 +3896,7 @@
         <v>5.4</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>25</v>
@@ -3898,10 +3907,10 @@
         <v>6.1</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
@@ -3909,7 +3918,7 @@
         <v>6.2</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>25</v>
@@ -3920,7 +3929,7 @@
         <v>6.3</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>25</v>
@@ -3931,7 +3940,7 @@
         <v>6.4</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>25</v>
@@ -3942,7 +3951,7 @@
         <v>6.5</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>25</v>
@@ -3953,7 +3962,7 @@
         <v>7.1</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>25</v>
@@ -3964,7 +3973,7 @@
         <v>7.2</v>
       </c>
       <c r="B22" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>25</v>
@@ -3975,7 +3984,7 @@
         <v>7.3</v>
       </c>
       <c r="B23" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>25</v>
@@ -3986,7 +3995,7 @@
         <v>7.4</v>
       </c>
       <c r="B24" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>25</v>
@@ -3997,7 +4006,7 @@
         <v>8.1</v>
       </c>
       <c r="B25" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>25</v>
@@ -4008,7 +4017,7 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="B26" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>25</v>
@@ -4019,7 +4028,7 @@
         <v>9.1</v>
       </c>
       <c r="B27" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>25</v>
@@ -4030,7 +4039,7 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="B28" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>25</v>
@@ -4041,7 +4050,7 @@
         <v>9.3000000000000007</v>
       </c>
       <c r="B29" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>25</v>
@@ -4052,7 +4061,7 @@
         <v>10.1</v>
       </c>
       <c r="B30" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>25</v>
@@ -4063,7 +4072,7 @@
         <v>10.199999999999999</v>
       </c>
       <c r="B31" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>25</v>
